--- a/mlef_pipeline/results/DCR/C23/RWD_DP_FMRAD/rwd-only/results.xlsx
+++ b/mlef_pipeline/results/DCR/C23/RWD_DP_FMRAD/rwd-only/results.xlsx
@@ -468,26 +468,26 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0.63 ± 0.07</t>
+          <t>0.59 ± 0.07</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.54 ± 0.07</t>
+          <t>0.52 ± 0.07</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.63 ± 0.13</t>
+          <t>0.60 ± 0.15</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.48 ± 0.17</t>
+          <t>0.48 ± 0.19</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="3">
@@ -498,22 +498,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0.66 ± 0.20</t>
+          <t>0.67 ± 0.16</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -528,22 +528,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.71 ± 0.12</t>
+          <t>0.76 ± 0.11</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="F4" t="n">

--- a/mlef_pipeline/results/DCR/C23/RWD_DP_FMRAD/rwd-only/results.xlsx
+++ b/mlef_pipeline/results/DCR/C23/RWD_DP_FMRAD/rwd-only/results.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -468,22 +468,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0.59 ± 0.07</t>
+          <t>0.63 ± 0.07</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.52 ± 0.07</t>
+          <t>0.56 ± 0.05</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.60 ± 0.15</t>
+          <t>0.64 ± 0.13</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.48 ± 0.19</t>
+          <t>0.49 ± 0.10</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -498,17 +498,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0.67 ± 0.16</t>
+          <t>0.58 ± 0.17</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.76 ± 0.11</t>
+          <t>0.62 ± 0.14</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -538,12 +538,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="F4" t="n">
